--- a/artfynd/A 33301-2026 artfynd.xlsx
+++ b/artfynd/A 33301-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ112"/>
+  <dimension ref="A1:AZ113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11072,53 +11072,56 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135941456</v>
+        <v>135970265</v>
       </c>
       <c r="B90" t="n">
-        <v>57167</v>
+        <v>57980</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gåstjärnarna, Dlr</t>
+          <t>Gåstjärnarna, Stor-Vasselnäs, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>459793</v>
+        <v>459697</v>
       </c>
       <c r="R90" t="n">
-        <v>6790040</v>
+        <v>6790052</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11145,19 +11148,9 @@
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11183,16 +11176,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941456</t>
+          <t>https://artportalen.se/Sighting/135970265</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135941484</v>
+        <v>135941456</v>
       </c>
       <c r="B91" t="n">
-        <v>58601</v>
+        <v>57167</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11200,16 +11193,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103041</v>
+        <v>100138</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bergfink</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fringilla montifringilla</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -11220,7 +11213,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11229,13 +11222,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>459828</v>
+        <v>459793</v>
       </c>
       <c r="R91" t="n">
-        <v>6790163</v>
+        <v>6790040</v>
       </c>
       <c r="S91" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11264,7 +11257,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11274,7 +11267,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11300,16 +11293,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941484</t>
+          <t>https://artportalen.se/Sighting/135941456</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135941424</v>
+        <v>135941484</v>
       </c>
       <c r="B92" t="n">
-        <v>8461</v>
+        <v>58601</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11317,27 +11310,27 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>103041</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11346,13 +11339,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>460098</v>
+        <v>459828</v>
       </c>
       <c r="R92" t="n">
-        <v>6790851</v>
+        <v>6790163</v>
       </c>
       <c r="S92" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11381,7 +11374,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11391,7 +11384,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11417,13 +11410,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941424</t>
+          <t>https://artportalen.se/Sighting/135941484</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135941468</v>
+        <v>135941424</v>
       </c>
       <c r="B93" t="n">
         <v>8461</v>
@@ -11463,10 +11456,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>459819</v>
+        <v>460098</v>
       </c>
       <c r="R93" t="n">
-        <v>6789992</v>
+        <v>6790851</v>
       </c>
       <c r="S93" t="n">
         <v>8</v>
@@ -11498,7 +11491,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11508,7 +11501,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11519,26 +11512,6 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
@@ -11554,13 +11527,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941468</t>
+          <t>https://artportalen.se/Sighting/135941424</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135941477</v>
+        <v>135941468</v>
       </c>
       <c r="B94" t="n">
         <v>8461</v>
@@ -11600,10 +11573,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>459951</v>
+        <v>459819</v>
       </c>
       <c r="R94" t="n">
-        <v>6790200</v>
+        <v>6789992</v>
       </c>
       <c r="S94" t="n">
         <v>8</v>
@@ -11635,7 +11608,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11645,7 +11618,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11656,6 +11629,26 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM94" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -11671,13 +11664,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941477</t>
+          <t>https://artportalen.se/Sighting/135941468</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135941489</v>
+        <v>135941477</v>
       </c>
       <c r="B95" t="n">
         <v>8461</v>
@@ -11717,13 +11710,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>459693</v>
+        <v>459951</v>
       </c>
       <c r="R95" t="n">
-        <v>6790134</v>
+        <v>6790200</v>
       </c>
       <c r="S95" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11752,7 +11745,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11762,7 +11755,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11788,13 +11781,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941489</t>
+          <t>https://artportalen.se/Sighting/135941477</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135941494</v>
+        <v>135941489</v>
       </c>
       <c r="B96" t="n">
         <v>8461</v>
@@ -11834,13 +11827,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>459590</v>
+        <v>459693</v>
       </c>
       <c r="R96" t="n">
-        <v>6790151</v>
+        <v>6790134</v>
       </c>
       <c r="S96" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11869,7 +11862,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11879,7 +11872,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11905,13 +11898,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941494</t>
+          <t>https://artportalen.se/Sighting/135941489</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135941495</v>
+        <v>135941494</v>
       </c>
       <c r="B97" t="n">
         <v>8461</v>
@@ -11951,13 +11944,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>459588</v>
+        <v>459590</v>
       </c>
       <c r="R97" t="n">
-        <v>6790152</v>
+        <v>6790151</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11986,7 +11979,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11996,7 +11989,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12022,13 +12015,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941495</t>
+          <t>https://artportalen.se/Sighting/135941494</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135941498</v>
+        <v>135941495</v>
       </c>
       <c r="B98" t="n">
         <v>8461</v>
@@ -12068,10 +12061,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>459573</v>
+        <v>459588</v>
       </c>
       <c r="R98" t="n">
-        <v>6790142</v>
+        <v>6790152</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -12103,7 +12096,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12113,7 +12106,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12139,13 +12132,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941498</t>
+          <t>https://artportalen.se/Sighting/135941495</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135944895</v>
+        <v>135941498</v>
       </c>
       <c r="B99" t="n">
         <v>8461</v>
@@ -12185,13 +12178,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>459816</v>
+        <v>459573</v>
       </c>
       <c r="R99" t="n">
-        <v>6790008</v>
+        <v>6790142</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12220,7 +12213,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12230,7 +12223,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12241,43 +12234,28 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944895</t>
+          <t>https://artportalen.se/Sighting/135941498</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135944896</v>
+        <v>135944895</v>
       </c>
       <c r="B100" t="n">
         <v>8461</v>
@@ -12317,13 +12295,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>459824</v>
+        <v>459816</v>
       </c>
       <c r="R100" t="n">
         <v>6790008</v>
       </c>
       <c r="S100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12352,7 +12330,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12362,7 +12340,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12403,13 +12381,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944896</t>
+          <t>https://artportalen.se/Sighting/135944895</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135944899</v>
+        <v>135944896</v>
       </c>
       <c r="B101" t="n">
         <v>8461</v>
@@ -12449,10 +12427,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>459829</v>
+        <v>459824</v>
       </c>
       <c r="R101" t="n">
-        <v>6790085</v>
+        <v>6790008</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12484,7 +12462,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12494,7 +12472,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12535,13 +12513,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944899</t>
+          <t>https://artportalen.se/Sighting/135944896</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135944902</v>
+        <v>135944899</v>
       </c>
       <c r="B102" t="n">
         <v>8461</v>
@@ -12570,19 +12548,24 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Gåstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>459880</v>
+        <v>459829</v>
       </c>
       <c r="R102" t="n">
-        <v>6790200</v>
+        <v>6790085</v>
       </c>
       <c r="S102" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12611,7 +12594,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12621,7 +12604,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12633,14 +12616,19 @@
       <c r="AG102" t="b">
         <v>0</v>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12657,13 +12645,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944902</t>
+          <t>https://artportalen.se/Sighting/135944899</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135944904</v>
+        <v>135944902</v>
       </c>
       <c r="B103" t="n">
         <v>8461</v>
@@ -12692,24 +12680,19 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Gåstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>459634</v>
+        <v>459880</v>
       </c>
       <c r="R103" t="n">
-        <v>6790173</v>
+        <v>6790200</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12738,7 +12721,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12748,7 +12731,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12784,44 +12767,44 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944904</t>
+          <t>https://artportalen.se/Sighting/135944902</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135941438</v>
+        <v>135944904</v>
       </c>
       <c r="B104" t="n">
-        <v>56544</v>
+        <v>8461</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>206004</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -12830,13 +12813,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>460104</v>
+        <v>459634</v>
       </c>
       <c r="R104" t="n">
-        <v>6790638</v>
+        <v>6790173</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12865,7 +12848,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12875,7 +12858,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12886,31 +12869,41 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941438</t>
+          <t>https://artportalen.se/Sighting/135944904</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135941428</v>
+        <v>135941438</v>
       </c>
       <c r="B105" t="n">
-        <v>79199</v>
+        <v>56544</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12918,37 +12911,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>206004</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Gåstjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>460089</v>
+        <v>460104</v>
       </c>
       <c r="R105" t="n">
-        <v>6790868</v>
+        <v>6790638</v>
       </c>
       <c r="S105" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12977,7 +12975,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12987,7 +12985,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12998,16 +12996,6 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
@@ -13023,13 +13011,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941428</t>
+          <t>https://artportalen.se/Sighting/135941438</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135941457</v>
+        <v>135941428</v>
       </c>
       <c r="B106" t="n">
         <v>79199</v>
@@ -13064,10 +13052,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>459778</v>
+        <v>460089</v>
       </c>
       <c r="R106" t="n">
-        <v>6790013</v>
+        <v>6790868</v>
       </c>
       <c r="S106" t="n">
         <v>8</v>
@@ -13099,7 +13087,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13109,7 +13097,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13145,13 +13133,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941457</t>
+          <t>https://artportalen.se/Sighting/135941428</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135941464</v>
+        <v>135941457</v>
       </c>
       <c r="B107" t="n">
         <v>79199</v>
@@ -13186,13 +13174,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>459806</v>
+        <v>459778</v>
       </c>
       <c r="R107" t="n">
-        <v>6789981</v>
+        <v>6790013</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13221,7 +13209,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13231,7 +13219,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13242,6 +13230,16 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
@@ -13257,13 +13255,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941464</t>
+          <t>https://artportalen.se/Sighting/135941457</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135941502</v>
+        <v>135941464</v>
       </c>
       <c r="B108" t="n">
         <v>79199</v>
@@ -13298,13 +13296,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>459567</v>
+        <v>459806</v>
       </c>
       <c r="R108" t="n">
-        <v>6790111</v>
+        <v>6789981</v>
       </c>
       <c r="S108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13333,7 +13331,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13343,7 +13341,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13369,13 +13367,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135941502</t>
+          <t>https://artportalen.se/Sighting/135941464</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135944889</v>
+        <v>135941502</v>
       </c>
       <c r="B109" t="n">
         <v>79199</v>
@@ -13410,13 +13408,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>459785</v>
+        <v>459567</v>
       </c>
       <c r="R109" t="n">
-        <v>6790068</v>
+        <v>6790111</v>
       </c>
       <c r="S109" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13445,7 +13443,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13455,12 +13453,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>12:59</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Kolad högstubbe</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13471,38 +13464,28 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Elisa Andersson</t>
+          <t>Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944889</t>
+          <t>https://artportalen.se/Sighting/135941502</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135944891</v>
+        <v>135944889</v>
       </c>
       <c r="B110" t="n">
         <v>79199</v>
@@ -13537,13 +13520,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>459782</v>
+        <v>459785</v>
       </c>
       <c r="R110" t="n">
-        <v>6790013</v>
+        <v>6790068</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13572,7 +13555,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13582,7 +13565,12 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Kolad högstubbe</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13596,12 +13584,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>Branddödat träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>Fire killed tree</t>
+          <t>Standing dead tree/snags</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -13618,13 +13606,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944891</t>
+          <t>https://artportalen.se/Sighting/135944889</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135944903</v>
+        <v>135944891</v>
       </c>
       <c r="B111" t="n">
         <v>79199</v>
@@ -13659,13 +13647,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>459829</v>
+        <v>459782</v>
       </c>
       <c r="R111" t="n">
-        <v>6790153</v>
+        <v>6790013</v>
       </c>
       <c r="S111" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13694,7 +13682,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13704,7 +13692,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13740,16 +13728,16 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944903</t>
+          <t>https://artportalen.se/Sighting/135944891</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135944876</v>
+        <v>135944903</v>
       </c>
       <c r="B112" t="n">
-        <v>80031</v>
+        <v>79199</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13757,21 +13745,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13781,13 +13769,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>460161</v>
+        <v>459829</v>
       </c>
       <c r="R112" t="n">
-        <v>6790782</v>
+        <v>6790153</v>
       </c>
       <c r="S112" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13816,7 +13804,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13826,7 +13814,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13861,6 +13849,128 @@
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135944903</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>135944876</v>
+      </c>
+      <c r="B113" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Gåstjärnarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>460161</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6790782</v>
+      </c>
+      <c r="S113" t="n">
+        <v>12</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Branddödat träd</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Fire killed tree</t>
+        </is>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135944876</t>
         </is>
@@ -13979,6 +14089,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33301-2026 artfynd.xlsx
+++ b/artfynd/A 33301-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941442</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135944879</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135941426</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>135941443</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>135941444</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135941471</v>
       </c>
       <c r="B7" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135944890</v>
       </c>
       <c r="B8" t="n">
-        <v>81423</v>
+        <v>81425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>135941500</v>
       </c>
       <c r="B9" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135941396</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>135941398</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>135941400</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135941402</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135941403</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135941408</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135941413</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>135941414</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135941417</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>135941418</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>135941421</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135941429</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135941431</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135941434</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135941435</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>135941436</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135941437</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>135941439</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>135941440</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>135941445</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135941449</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135941452</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135941453</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135941455</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135941460</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135941461</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135941474</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135941475</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135941478</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135941483</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135941485</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135941487</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135941488</v>
       </c>
       <c r="B42" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135941490</v>
       </c>
       <c r="B43" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135941499</v>
       </c>
       <c r="B44" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135941503</v>
       </c>
       <c r="B45" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135941504</v>
       </c>
       <c r="B46" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135944870</v>
       </c>
       <c r="B47" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>135944871</v>
       </c>
       <c r="B48" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>135944873</v>
       </c>
       <c r="B49" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>135944874</v>
       </c>
       <c r="B50" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135944877</v>
       </c>
       <c r="B51" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>135944878</v>
       </c>
       <c r="B52" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>135944882</v>
       </c>
       <c r="B53" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>135944886</v>
       </c>
       <c r="B54" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>135944893</v>
       </c>
       <c r="B55" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>135944897</v>
       </c>
       <c r="B56" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>135944900</v>
       </c>
       <c r="B57" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>135944901</v>
       </c>
       <c r="B58" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>135944910</v>
       </c>
       <c r="B59" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>135941423</v>
       </c>
       <c r="B60" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>135941427</v>
       </c>
       <c r="B61" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>135941448</v>
       </c>
       <c r="B62" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>135941459</v>
       </c>
       <c r="B63" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>135941466</v>
       </c>
       <c r="B64" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>135941501</v>
       </c>
       <c r="B65" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>135944875</v>
       </c>
       <c r="B66" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>135944909</v>
       </c>
       <c r="B67" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>135941411</v>
       </c>
       <c r="B68" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>135941412</v>
       </c>
       <c r="B69" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>135941422</v>
       </c>
       <c r="B70" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>135941425</v>
       </c>
       <c r="B71" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135941446</v>
       </c>
       <c r="B72" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135941450</v>
       </c>
       <c r="B73" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135941467</v>
       </c>
       <c r="B74" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>135941473</v>
       </c>
       <c r="B75" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>135941476</v>
       </c>
       <c r="B76" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>135941479</v>
       </c>
       <c r="B77" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>135941481</v>
       </c>
       <c r="B78" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>135941482</v>
       </c>
       <c r="B79" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>135944872</v>
       </c>
       <c r="B80" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>135944885</v>
       </c>
       <c r="B81" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>135944892</v>
       </c>
       <c r="B82" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>135944906</v>
       </c>
       <c r="B83" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>135944908</v>
       </c>
       <c r="B84" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>135941433</v>
       </c>
       <c r="B85" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>135941391</v>
       </c>
       <c r="B86" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>135941497</v>
       </c>
       <c r="B87" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135944905</v>
       </c>
       <c r="B88" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>135941409</v>
       </c>
       <c r="B89" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>135970265</v>
       </c>
       <c r="B90" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>135941456</v>
       </c>
       <c r="B91" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>135941484</v>
       </c>
       <c r="B92" t="n">
-        <v>58601</v>
+        <v>58603</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>135941424</v>
       </c>
       <c r="B93" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>135941468</v>
       </c>
       <c r="B94" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>135941477</v>
       </c>
       <c r="B95" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>135941489</v>
       </c>
       <c r="B96" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>135941494</v>
       </c>
       <c r="B97" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>135941495</v>
       </c>
       <c r="B98" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>135941498</v>
       </c>
       <c r="B99" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12258,7 +12258,7 @@
         <v>135944895</v>
       </c>
       <c r="B100" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>135944896</v>
       </c>
       <c r="B101" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>135944899</v>
       </c>
       <c r="B102" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>135944902</v>
       </c>
       <c r="B103" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12776,7 +12776,7 @@
         <v>135944904</v>
       </c>
       <c r="B104" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>135941438</v>
       </c>
       <c r="B105" t="n">
-        <v>56544</v>
+        <v>56546</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135941428</v>
       </c>
       <c r="B106" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>135941457</v>
       </c>
       <c r="B107" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>135941464</v>
       </c>
       <c r="B108" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>135941502</v>
       </c>
       <c r="B109" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>135944889</v>
       </c>
       <c r="B110" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>135944891</v>
       </c>
       <c r="B111" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>135944903</v>
       </c>
       <c r="B112" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>135944876</v>
       </c>
       <c r="B113" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 33301-2026 artfynd.xlsx
+++ b/artfynd/A 33301-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941442</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135944879</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135941426</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>135941443</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>135941444</v>
       </c>
       <c r="B6" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135941471</v>
       </c>
       <c r="B7" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135944890</v>
       </c>
       <c r="B8" t="n">
-        <v>81425</v>
+        <v>81426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>135941500</v>
       </c>
       <c r="B9" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135941396</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>135941398</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>135941400</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135941402</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135941403</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135941408</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135941413</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>135941414</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135941417</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>135941418</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>135941421</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135941429</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135941431</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135941434</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135941435</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>135941436</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135941437</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>135941439</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>135941440</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>135941445</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135941449</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135941452</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135941453</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135941455</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135941460</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135941461</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135941474</v>
       </c>
       <c r="B36" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135941475</v>
       </c>
       <c r="B37" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135941478</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135941483</v>
       </c>
       <c r="B39" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135941485</v>
       </c>
       <c r="B40" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135941487</v>
       </c>
       <c r="B41" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135941488</v>
       </c>
       <c r="B42" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135941490</v>
       </c>
       <c r="B43" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135941499</v>
       </c>
       <c r="B44" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135941503</v>
       </c>
       <c r="B45" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135941504</v>
       </c>
       <c r="B46" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135944870</v>
       </c>
       <c r="B47" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>135944871</v>
       </c>
       <c r="B48" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>135944873</v>
       </c>
       <c r="B49" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>135944874</v>
       </c>
       <c r="B50" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135944877</v>
       </c>
       <c r="B51" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>135944878</v>
       </c>
       <c r="B52" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>135944882</v>
       </c>
       <c r="B53" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>135944886</v>
       </c>
       <c r="B54" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>135944893</v>
       </c>
       <c r="B55" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>135944897</v>
       </c>
       <c r="B56" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>135944900</v>
       </c>
       <c r="B57" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>135944901</v>
       </c>
       <c r="B58" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>135944910</v>
       </c>
       <c r="B59" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>135941423</v>
       </c>
       <c r="B60" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>135941427</v>
       </c>
       <c r="B61" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>135941448</v>
       </c>
       <c r="B62" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>135941459</v>
       </c>
       <c r="B63" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>135941466</v>
       </c>
       <c r="B64" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>135941501</v>
       </c>
       <c r="B65" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>135944875</v>
       </c>
       <c r="B66" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>135944909</v>
       </c>
       <c r="B67" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>135941411</v>
       </c>
       <c r="B68" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>135941412</v>
       </c>
       <c r="B69" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>135941422</v>
       </c>
       <c r="B70" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>135941425</v>
       </c>
       <c r="B71" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135941446</v>
       </c>
       <c r="B72" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135941450</v>
       </c>
       <c r="B73" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135941467</v>
       </c>
       <c r="B74" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>135941473</v>
       </c>
       <c r="B75" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>135941476</v>
       </c>
       <c r="B76" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>135941479</v>
       </c>
       <c r="B77" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>135941481</v>
       </c>
       <c r="B78" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>135941482</v>
       </c>
       <c r="B79" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>135944872</v>
       </c>
       <c r="B80" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>135944885</v>
       </c>
       <c r="B81" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>135944892</v>
       </c>
       <c r="B82" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>135944906</v>
       </c>
       <c r="B83" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>135944908</v>
       </c>
       <c r="B84" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>135941433</v>
       </c>
       <c r="B85" t="n">
-        <v>80452</v>
+        <v>80453</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135941428</v>
       </c>
       <c r="B106" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>135941457</v>
       </c>
       <c r="B107" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>135941464</v>
       </c>
       <c r="B108" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>135941502</v>
       </c>
       <c r="B109" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>135944889</v>
       </c>
       <c r="B110" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>135944891</v>
       </c>
       <c r="B111" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>135944903</v>
       </c>
       <c r="B112" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>135944876</v>
       </c>
       <c r="B113" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 33301-2026 artfynd.xlsx
+++ b/artfynd/A 33301-2026 artfynd.xlsx
@@ -1557,7 +1557,7 @@
         <v>135941500</v>
       </c>
       <c r="B9" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33301-2026 artfynd.xlsx
+++ b/artfynd/A 33301-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941442</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135944879</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135941426</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>135941443</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>135941444</v>
       </c>
       <c r="B6" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135941471</v>
       </c>
       <c r="B7" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135944890</v>
       </c>
       <c r="B8" t="n">
-        <v>81426</v>
+        <v>81427</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>135941500</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135941396</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>135941398</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>135941400</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135941402</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135941403</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135941408</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135941413</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>135941414</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135941417</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>135941418</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>135941421</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135941429</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135941431</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135941434</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135941435</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>135941436</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135941437</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>135941439</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>135941440</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>135941445</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135941449</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135941452</v>
       </c>
       <c r="B31" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135941453</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135941455</v>
       </c>
       <c r="B33" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135941460</v>
       </c>
       <c r="B34" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135941461</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135941474</v>
       </c>
       <c r="B36" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135941475</v>
       </c>
       <c r="B37" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135941478</v>
       </c>
       <c r="B38" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135941483</v>
       </c>
       <c r="B39" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135941485</v>
       </c>
       <c r="B40" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135941487</v>
       </c>
       <c r="B41" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135941488</v>
       </c>
       <c r="B42" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135941490</v>
       </c>
       <c r="B43" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135941499</v>
       </c>
       <c r="B44" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135941503</v>
       </c>
       <c r="B45" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135941504</v>
       </c>
       <c r="B46" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135944870</v>
       </c>
       <c r="B47" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>135944871</v>
       </c>
       <c r="B48" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>135944873</v>
       </c>
       <c r="B49" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>135944874</v>
       </c>
       <c r="B50" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135944877</v>
       </c>
       <c r="B51" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>135944878</v>
       </c>
       <c r="B52" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>135944882</v>
       </c>
       <c r="B53" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>135944886</v>
       </c>
       <c r="B54" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>135944893</v>
       </c>
       <c r="B55" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>135944897</v>
       </c>
       <c r="B56" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>135944900</v>
       </c>
       <c r="B57" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>135944901</v>
       </c>
       <c r="B58" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>135944910</v>
       </c>
       <c r="B59" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>135941423</v>
       </c>
       <c r="B60" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>135941427</v>
       </c>
       <c r="B61" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>135941448</v>
       </c>
       <c r="B62" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>135941459</v>
       </c>
       <c r="B63" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>135941466</v>
       </c>
       <c r="B64" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>135941501</v>
       </c>
       <c r="B65" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>135944875</v>
       </c>
       <c r="B66" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>135944909</v>
       </c>
       <c r="B67" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>135941411</v>
       </c>
       <c r="B68" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>135941412</v>
       </c>
       <c r="B69" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>135941422</v>
       </c>
       <c r="B70" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>135941425</v>
       </c>
       <c r="B71" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135941446</v>
       </c>
       <c r="B72" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135941450</v>
       </c>
       <c r="B73" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135941467</v>
       </c>
       <c r="B74" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>135941473</v>
       </c>
       <c r="B75" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>135941476</v>
       </c>
       <c r="B76" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>135941479</v>
       </c>
       <c r="B77" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>135941481</v>
       </c>
       <c r="B78" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>135941482</v>
       </c>
       <c r="B79" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>135944872</v>
       </c>
       <c r="B80" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>135944885</v>
       </c>
       <c r="B81" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>135944892</v>
       </c>
       <c r="B82" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>135944906</v>
       </c>
       <c r="B83" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>135944908</v>
       </c>
       <c r="B84" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>135941433</v>
       </c>
       <c r="B85" t="n">
-        <v>80453</v>
+        <v>80454</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>135941391</v>
       </c>
       <c r="B86" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>135941497</v>
       </c>
       <c r="B87" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135944905</v>
       </c>
       <c r="B88" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>135941409</v>
       </c>
       <c r="B89" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>135970265</v>
       </c>
       <c r="B90" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>135941456</v>
       </c>
       <c r="B91" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>135941484</v>
       </c>
       <c r="B92" t="n">
-        <v>58603</v>
+        <v>58604</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>135941438</v>
       </c>
       <c r="B105" t="n">
-        <v>56546</v>
+        <v>56547</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135941428</v>
       </c>
       <c r="B106" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>135941457</v>
       </c>
       <c r="B107" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>135941464</v>
       </c>
       <c r="B108" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>135941502</v>
       </c>
       <c r="B109" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>135944889</v>
       </c>
       <c r="B110" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>135944891</v>
       </c>
       <c r="B111" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>135944903</v>
       </c>
       <c r="B112" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>135944876</v>
       </c>
       <c r="B113" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 33301-2026 artfynd.xlsx
+++ b/artfynd/A 33301-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941442</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135944879</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135941426</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>135941443</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>135941444</v>
       </c>
       <c r="B6" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135941471</v>
       </c>
       <c r="B7" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135944890</v>
       </c>
       <c r="B8" t="n">
-        <v>81427</v>
+        <v>81431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>135941500</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135941396</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>135941398</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>135941400</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135941402</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135941403</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135941408</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135941413</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>135941414</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135941417</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>135941418</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>135941421</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135941429</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135941431</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135941434</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135941435</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>135941436</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135941437</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>135941439</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>135941440</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>135941445</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135941449</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135941452</v>
       </c>
       <c r="B31" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135941453</v>
       </c>
       <c r="B32" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135941455</v>
       </c>
       <c r="B33" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135941460</v>
       </c>
       <c r="B34" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135941461</v>
       </c>
       <c r="B35" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135941474</v>
       </c>
       <c r="B36" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135941475</v>
       </c>
       <c r="B37" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135941478</v>
       </c>
       <c r="B38" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135941483</v>
       </c>
       <c r="B39" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135941485</v>
       </c>
       <c r="B40" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135941487</v>
       </c>
       <c r="B41" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135941488</v>
       </c>
       <c r="B42" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135941490</v>
       </c>
       <c r="B43" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135941499</v>
       </c>
       <c r="B44" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135941503</v>
       </c>
       <c r="B45" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135941504</v>
       </c>
       <c r="B46" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135944870</v>
       </c>
       <c r="B47" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>135944871</v>
       </c>
       <c r="B48" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>135944873</v>
       </c>
       <c r="B49" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>135944874</v>
       </c>
       <c r="B50" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135944877</v>
       </c>
       <c r="B51" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>135944878</v>
       </c>
       <c r="B52" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>135944882</v>
       </c>
       <c r="B53" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>135944886</v>
       </c>
       <c r="B54" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>135944893</v>
       </c>
       <c r="B55" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>135944897</v>
       </c>
       <c r="B56" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>135944900</v>
       </c>
       <c r="B57" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>135944901</v>
       </c>
       <c r="B58" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>135944910</v>
       </c>
       <c r="B59" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>135941423</v>
       </c>
       <c r="B60" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>135941427</v>
       </c>
       <c r="B61" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>135941448</v>
       </c>
       <c r="B62" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>135941459</v>
       </c>
       <c r="B63" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>135941466</v>
       </c>
       <c r="B64" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>135941501</v>
       </c>
       <c r="B65" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>135944875</v>
       </c>
       <c r="B66" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>135944909</v>
       </c>
       <c r="B67" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>135941411</v>
       </c>
       <c r="B68" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>135941412</v>
       </c>
       <c r="B69" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>135941422</v>
       </c>
       <c r="B70" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>135941425</v>
       </c>
       <c r="B71" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135941446</v>
       </c>
       <c r="B72" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135941450</v>
       </c>
       <c r="B73" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135941467</v>
       </c>
       <c r="B74" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>135941473</v>
       </c>
       <c r="B75" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>135941476</v>
       </c>
       <c r="B76" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>135941479</v>
       </c>
       <c r="B77" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>135941481</v>
       </c>
       <c r="B78" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>135941482</v>
       </c>
       <c r="B79" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>135944872</v>
       </c>
       <c r="B80" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>135944885</v>
       </c>
       <c r="B81" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>135944892</v>
       </c>
       <c r="B82" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>135944906</v>
       </c>
       <c r="B83" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>135944908</v>
       </c>
       <c r="B84" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>135941433</v>
       </c>
       <c r="B85" t="n">
-        <v>80454</v>
+        <v>80458</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>135941391</v>
       </c>
       <c r="B86" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>135941497</v>
       </c>
       <c r="B87" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135944905</v>
       </c>
       <c r="B88" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>135941409</v>
       </c>
       <c r="B89" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>135970265</v>
       </c>
       <c r="B90" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>135941456</v>
       </c>
       <c r="B91" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>135941484</v>
       </c>
       <c r="B92" t="n">
-        <v>58604</v>
+        <v>58608</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>135941438</v>
       </c>
       <c r="B105" t="n">
-        <v>56547</v>
+        <v>56551</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135941428</v>
       </c>
       <c r="B106" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>135941457</v>
       </c>
       <c r="B107" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>135941464</v>
       </c>
       <c r="B108" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>135941502</v>
       </c>
       <c r="B109" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>135944889</v>
       </c>
       <c r="B110" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>135944891</v>
       </c>
       <c r="B111" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>135944903</v>
       </c>
       <c r="B112" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>135944876</v>
       </c>
       <c r="B113" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 33301-2026 artfynd.xlsx
+++ b/artfynd/A 33301-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135941442</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>135944879</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -942,7 +942,7 @@
         <v>135941426</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
         <v>135941443</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>135941444</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>135941471</v>
       </c>
       <c r="B7" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>135944890</v>
       </c>
       <c r="B8" t="n">
-        <v>81431</v>
+        <v>81432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>135941500</v>
       </c>
       <c r="B9" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135941396</v>
       </c>
       <c r="B10" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>135941398</v>
       </c>
       <c r="B11" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>135941400</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
         <v>135941402</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135941403</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135941408</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>135941413</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>135941414</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
         <v>135941417</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>135941418</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         <v>135941421</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>135941429</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>135941431</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>135941434</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3237,7 +3237,7 @@
         <v>135941435</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>135941436</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         <v>135941437</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>135941439</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>135941440</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>135941445</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3917,7 +3917,7 @@
         <v>135941449</v>
       </c>
       <c r="B30" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>135941452</v>
       </c>
       <c r="B31" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4145,7 +4145,7 @@
         <v>135941453</v>
       </c>
       <c r="B32" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>135941455</v>
       </c>
       <c r="B33" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>135941460</v>
       </c>
       <c r="B34" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>135941461</v>
       </c>
       <c r="B35" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>135941474</v>
       </c>
       <c r="B36" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>135941475</v>
       </c>
       <c r="B37" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>135941478</v>
       </c>
       <c r="B38" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
         <v>135941483</v>
       </c>
       <c r="B39" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
         <v>135941485</v>
       </c>
       <c r="B40" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>135941487</v>
       </c>
       <c r="B41" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>135941488</v>
       </c>
       <c r="B42" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>135941490</v>
       </c>
       <c r="B43" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         <v>135941499</v>
       </c>
       <c r="B44" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>135941503</v>
       </c>
       <c r="B45" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5713,7 +5713,7 @@
         <v>135941504</v>
       </c>
       <c r="B46" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>135944870</v>
       </c>
       <c r="B47" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>135944871</v>
       </c>
       <c r="B48" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>135944873</v>
       </c>
       <c r="B49" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
         <v>135944874</v>
       </c>
       <c r="B50" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>135944877</v>
       </c>
       <c r="B51" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>135944878</v>
       </c>
       <c r="B52" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>135944882</v>
       </c>
       <c r="B53" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>135944886</v>
       </c>
       <c r="B54" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6881,7 +6881,7 @@
         <v>135944893</v>
       </c>
       <c r="B55" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7013,7 +7013,7 @@
         <v>135944897</v>
       </c>
       <c r="B56" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7145,7 +7145,7 @@
         <v>135944900</v>
       </c>
       <c r="B57" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7277,7 +7277,7 @@
         <v>135944901</v>
       </c>
       <c r="B58" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7409,7 +7409,7 @@
         <v>135944910</v>
       </c>
       <c r="B59" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>135941423</v>
       </c>
       <c r="B60" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>135941427</v>
       </c>
       <c r="B61" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         <v>135941448</v>
       </c>
       <c r="B62" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>135941459</v>
       </c>
       <c r="B63" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>135941466</v>
       </c>
       <c r="B64" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>135941501</v>
       </c>
       <c r="B65" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8258,7 +8258,7 @@
         <v>135944875</v>
       </c>
       <c r="B66" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>135944909</v>
       </c>
       <c r="B67" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         <v>135941411</v>
       </c>
       <c r="B68" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>135941412</v>
       </c>
       <c r="B69" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8726,7 +8726,7 @@
         <v>135941422</v>
       </c>
       <c r="B70" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>135941425</v>
       </c>
       <c r="B71" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>135941446</v>
       </c>
       <c r="B72" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>135941450</v>
       </c>
       <c r="B73" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>135941467</v>
       </c>
       <c r="B74" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>135941473</v>
       </c>
       <c r="B75" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         <v>135941476</v>
       </c>
       <c r="B76" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9520,7 +9520,7 @@
         <v>135941479</v>
       </c>
       <c r="B77" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>135941481</v>
       </c>
       <c r="B78" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>135941482</v>
       </c>
       <c r="B79" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>135944872</v>
       </c>
       <c r="B80" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
         <v>135944885</v>
       </c>
       <c r="B81" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>135944892</v>
       </c>
       <c r="B82" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>135944906</v>
       </c>
       <c r="B83" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>135944908</v>
       </c>
       <c r="B84" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10466,7 +10466,7 @@
         <v>135941433</v>
       </c>
       <c r="B85" t="n">
-        <v>80458</v>
+        <v>80459</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>135941391</v>
       </c>
       <c r="B86" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>135941497</v>
       </c>
       <c r="B87" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10836,7 +10836,7 @@
         <v>135944905</v>
       </c>
       <c r="B88" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>135941409</v>
       </c>
       <c r="B89" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>135970265</v>
       </c>
       <c r="B90" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>135941456</v>
       </c>
       <c r="B91" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>135941484</v>
       </c>
       <c r="B92" t="n">
-        <v>58608</v>
+        <v>58609</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>135941438</v>
       </c>
       <c r="B105" t="n">
-        <v>56551</v>
+        <v>56552</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>135941428</v>
       </c>
       <c r="B106" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>135941457</v>
       </c>
       <c r="B107" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>135941464</v>
       </c>
       <c r="B108" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>135941502</v>
       </c>
       <c r="B109" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>135944889</v>
       </c>
       <c r="B110" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>135944891</v>
       </c>
       <c r="B111" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>135944903</v>
       </c>
       <c r="B112" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>135944876</v>
       </c>
       <c r="B113" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
